--- a/docs/격언.xlsx
+++ b/docs/격언.xlsx
@@ -583,24 +583,96 @@
           <t>君者盂也，盂方而水方；君者槃也，槃圓而水圓</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>A square bowl makes the water square; a round bowl makes it round</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, The Way of the Lord</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>君は盂なり、盂方なれば水方なり。君は槃なり、槃円なれば水円なり</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>『荀子』君道</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>君者盂也，盂方而水方；君者槃也，槃圓而水圓</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>《荀子·君道》</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>君者盂也，盂方而水方；君者槃也，槃圆而水圆</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>《荀子·君道》</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Tigela quadrada, água quadrada; tigela redonda, água redonda</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, O caminho do soberano</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Tigela quadrada, água quadrada; tigela redonda, água redonda</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, O caminho do soberano</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Ciotola quadrata, acqua quadrata; ciotola rotonda, acqua rotonda</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, La via del sovrano</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Cuenco cuadrado, agua cuadrada; cuenco redondo, agua redonda</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, El camino del soberano</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Аяга дөрвөлжин бол ус дөрвөлжин, аяга дугуй бол ус дугуй</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Сюнь-цзы, «Эзэний зам»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -621,24 +693,96 @@
           <t>君者，舟也；庶人者，水也。水則載舟，水則覆舟</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The ruler is the boat, the people are the water. Water carries the boat, and overturns it</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, Duke Ai</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>君は舟なり、庶人は水なり。水は則ち舟を載せ、水は則ち舟を覆す</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>『荀子』哀公</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>君者，舟也；庶人者，水也。水則載舟，水則覆舟</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>《荀子·哀公》</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>君者，舟也；庶人者，水也。水则载舟，水则覆舟</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>《荀子·哀公》</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>O soberano é o barco; o povo, a água. A água sustenta o barco e também o vira</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, O duque Ai</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>O soberano é o barco; o povo, a água. A água sustenta o barco e também o vira</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, O duque Ai</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Il sovrano è la barca, il popolo è l'acqua: l'acqua regge la barca e la capovolge</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, Il duca Ai</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>El soberano es la barca; el pueblo, el agua. El agua sostiene la barca y también la vuelca</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Xunzi, El duque Ai</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Хаан бол завь, ард түмэн бол ус. Ус завийг даах ч, хөмрөх ч чадна</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Сюнь-цзы, «Ай гүн»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -659,24 +803,96 @@
           <t>己所不欲，勿施於人</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>What you do not wish for yourself, do not impose on others</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Analects, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>己の欲せざる所は人に施す勿かれ</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>『論語』衛霊公</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>己所不欲，勿施於人</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>《論語·衛靈公》</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>己所不欲，勿施于人</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>《论语·卫灵公》</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Não faça aos outros o que você não deseja para si</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não faças aos outros o que não queres para ti</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Ciò che non vuoi per te, non farlo agli altri</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Dialoghi, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>No hagas a los demás lo que no quieras para ti</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Analectas, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Өөрт хүсэхгүй зүйлээ бусдад бүү хий</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Лунь юй, «Вэй Лин гүн»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -697,24 +913,96 @@
           <t>過而不改，是謂過矣</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>To err and not to correct it: that is the true error</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Analects, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>過ちて改めざる、是を過ちと謂う</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>『論語』衛霊公</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>過而不改，是謂過矣</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>《論語·衛靈公》</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>过而不改，是谓过矣</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>《论语·卫灵公》</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Errar e não se corrigir: esse é o verdadeiro erro</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Errar e não se corrigir: eis o verdadeiro erro</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Sbagliare e non correggersi: questo è il vero errore</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Dialoghi, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Errar y no corregirse: ese es el verdadero error</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Analectas, Wei Ling Gong</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Алдаад засахгүй байх нь жинхэнэ алдаа мөн</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Лунь юй, «Вэй Лин гүн»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -735,24 +1023,96 @@
           <t>以不教民戰，是謂棄之</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>To lead an untrained people into war is to throw them away</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Analects, Zilu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>教えざる民を以て戦う、是れ之を棄つと謂う</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>『論語』子路</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>以不教民戰，是謂棄之</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>《論語·子路》</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>以不教民战，是谓弃之</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>《论语·子路》</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Levar à guerra um povo sem preparo é abandoná-lo</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Zilu</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Levar à guerra um povo sem preparação é abandoná-lo</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Analectos, Zilu</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Mandare in guerra un popolo non addestrato è abbandonarlo</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Dialoghi, Zilu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Llevar a la guerra a un pueblo sin instrucción es abandonarlo</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Analectas, Zilu</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Сургаагүй ардыг дайнд илгээх нь тэднийг хаяж буй хэрэг</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Лунь юй, «Цзы Лу»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -773,24 +1133,96 @@
           <t>大辯若訥</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n"/>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Great eloquence seems to stammer</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, Chapter 45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>大弁は訥なるが若し</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>『老子』第四十五章</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>大辯若訥</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>《老子》第四十五章</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>大辩若讷</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>《老子》第四十五章</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>A grande eloquência parece gagueira</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 45</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>A grande eloquência parece gaguez</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 45</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>La grande eloquenza sembra balbettio</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capitolo 45</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>La gran elocuencia parece balbuceo</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 45</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Их уран үг ээрэх мэт</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Лао-цзы, 45-р бүлэг</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -811,24 +1243,96 @@
           <t>知足不辱，知止不殆</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Know contentment and you avoid disgrace; know when to stop and you avoid danger</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, Chapter 44</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>足るを知れば辱められず、止まるを知れば殆うからず</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>『老子』第四十四章</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>知足不辱，知止不殆</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>《老子》第四十四章</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>知足不辱，知止不殆</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>《老子》第四十四章</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Quem sabe se contentar não sofre desonra; quem sabe parar não corre perigo</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 44</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Quem sabe contentar-se não sofre desonra; quem sabe parar não corre perigo</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 44</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Chi sa accontentarsi non conosce vergogna; chi sa fermarsi non corre pericoli</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capitolo 44</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Quien sabe contentarse no sufre deshonra; quien sabe detenerse no corre peligro</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Laozi, capítulo 44</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Ханахаа мэдвэл гутамшиггүй, зогсохоо мэдвэл аюулгүй</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Лао-цзы, 44-р бүлэг</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -849,24 +1353,96 @@
           <t>安而不忘危，存而不忘亡，治而不忘亂</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>In safety, do not forget danger; in order, do not forget disorder</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, Great Commentary II</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>安くして危うきを忘れず、存して亡ぶるを忘れず、治まりて乱るるを忘れず</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>『易経』繋辞下伝</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>安而不忘危，存而不忘亡，治而不忘亂</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>《周易·繫辭下》</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>安而不忘危，存而不忘亡，治而不忘乱</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>《周易·系辞下》</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Na paz, não se esqueça do perigo; na ordem, não se esqueça da desordem</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, Grande Comentário II</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Na paz, não esqueças o perigo; na ordem, não esqueças a desordem</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, Grande Comentário II</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Nella pace non scordare il pericolo; nell'ordine non scordare il disordine</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, Grande Commento II</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>En la paz, no olvides el peligro; en el orden, no olvides el desorden</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, Gran Comentario II</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Амар үедээ аюулыг бүү март, эмх цэгцтэй үедээ самууныг бүү март</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>И цзин, «Си цы», доод</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -887,24 +1463,96 @@
           <t>不作無益害有益，功乃成</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Do nothing useless to the harm of what is useful, and your work will succeed</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Book of Documents, The Hounds of Lü</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>無益を作して有益を害せざれば、功乃ち成る</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>『書経』旅獒</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>不作無益害有益，功乃成</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>《尚書·旅獒》</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>不作无益害有益，功乃成</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>《尚书·旅獒》</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Não prejudique o útil com o inútil, e a obra se cumprirá</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Livro dos Documentos, Os cães de Lü</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Não prejudiques o útil com o inútil, e a obra cumprir-se-á</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Livro dos Documentos, Os cães de Lü</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Non nuocere all'utile con l'inutile, e l'opera si compirà</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Libro dei Documenti, I cani di Lü</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>No dañes lo útil con lo inútil, y la obra se cumplirá</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Libro de los Documentos, Los perros de Lü</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Хэрэггүй зүйлээр хэрэгтэйг бүү гэмтээ, тэгвэл үйлс бүтнэ</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Шу цзин, «Люйн нохой»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -925,24 +1573,96 @@
           <t>禍福無門，唯人所召</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Calamity and blessing have no gate of their own; people alone call them in</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Zuo Zhuan, Duke Xiang, Year 23</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>禍福は門無し、唯だ人の召く所なり</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>『春秋左氏伝』襄公二十三年</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>禍福無門，唯人所召</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>《左傳·襄公二十三年》</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>祸福无门，唯人所召</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>《左传·襄公二十三年》</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>A desgraça e a fortuna não têm porta própria; só o homem as chama</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Zuo Zhuan, duque Xiang, ano 23</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>A desgraça e a fortuna não têm porta própria; só o homem as chama</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Zuo Zhuan, duque Xiang, ano 23</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Sventura e fortuna non hanno una porta; è l'uomo solo a chiamarle</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Zuo Zhuan, duca Xiang, anno 23</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>La desdicha y la dicha no tienen puerta propia; solo el hombre las llama</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Zuo Zhuan, duque Xiang, año 23</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Гай ба буян орох хаалгагүй, гагцхүү хүн өөрөө дууддаг</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Цзо чжуань, Сян гүний 23-р он</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -963,24 +1683,96 @@
           <t>千羊之皮，不如一狐之腋</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>The hides of a thousand sheep are not worth the armpit fur of a single fox</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Records of the Grand Historian, Lord Shang</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>千羊の皮は、一狐の腋に如かず</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>『史記』商君列伝</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>千羊之皮，不如一狐之腋</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>《史記·商君列傳》</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>千羊之皮，不如一狐之腋</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>《史记·商君列传》</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Mil peles de ovelha não valem o pelo da axila de uma só raposa</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Registros do Grande Historiador, Senhor Shang</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Mil peles de ovelha não valem o pelo da axila de uma só raposa</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Registos do Grande Historiador, Senhor Shang</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Mille pelli di pecora non valgono il pelo sotto l'ascella di una volpe</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Memorie storiche, Il signore di Shang</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Mil pieles de oveja no valen el pelo de la axila de un solo zorro</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Memorias históricas, El señor de Shang</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Мянган хонины арьс нэг үнэгний суганы үсэнд хүрэхгүй</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Түүхэн тэмдэглэл, «Шан Яны намтар»</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1001,24 +1793,96 @@
           <t>懍乎，若朽索之馭六馬</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Be as wary as one driving six horses with rotten reins</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Caution to the End (Confucius)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>懍乎として、朽索の六馬を馭するが若し</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』慎終（孔子）</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>懍乎，若朽索之馭六馬</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·慎終》（孔子）</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>懔乎，若朽索之驭六马</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·慎终》（孔子）</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Tema como quem conduz seis cavalos com rédeas podres</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudência até o fim (Confúcio)</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Teme como quem conduz seis cavalos com rédeas podres</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudência até ao fim (Confúcio)</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Abbi il timore di chi guida sei cavalli con redini marce</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudenza fino alla fine (Confucio)</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Ten el temor de quien guía seis caballos con riendas podridas</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudencia hasta el fin (Confucio)</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>Ялзарсан жолоогоор зургаан морь залах мэт болгоомжил</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Эцэст нь болгоомжлох» (Күнз)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1039,24 +1903,96 @@
           <t>吾心如秤，不能為人作輕重</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>My heart is like a scale: I cannot tip it lighter or heavier for anyone</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Zhuge Liang (Zhenguan Zhengyao, Impartiality)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>吾が心は秤の如し、人の為に軽重を作す能わず</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>諸葛亮（『貞観政要』公平）</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>吾心如秤，不能為人作輕重</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>諸葛亮（《貞觀政要·公平》）</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>吾心如秤，不能为人作轻重</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>诸葛亮（《贞观政要·公平》）</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Meu coração é como uma balança: não alivia nem agrava nada por ninguém</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Zhuge Liang (Zhenguan Zhengyao, Imparcialidade)</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>O meu coração é como uma balança: não alivia nem agrava nada por ninguém</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Zhuge Liang (Zhenguan Zhengyao, Imparcialidade)</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Il mio cuore è come una bilancia: non alleggerisce né appesantisce per nessuno</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Zhuge Liang (Zhenguan Zhengyao, Imparzialità)</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Mi corazón es como una balanza: no aligera ni agrava nada por nadie</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Zhuge Liang (Zhenguan Zhengyao, Imparcialidad)</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Миний сэтгэл жин мэт, хэний ч төлөө хөнгөн хүндийг өөрчилж чадахгүй</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Чжугэ Лян (Чжэньгуань чжэнъяо, «Шударга ёс»)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1077,24 +2013,96 @@
           <t>非知之難，行之為難；非行之難，終之斯難</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Doing is harder than knowing, and finishing is harder than doing</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Caution to the End (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>之を知るの難きに非ず、之を行うを難しと為す。之を行うの難きに非ず、之を終うること斯れ難し</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』慎終（魏徴）</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>非知之難，行之為難；非行之難，終之斯難</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·慎終》（魏徵）</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>非知之难，行之为难；非行之难，终之斯难</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·慎终》（魏征）</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Fazer é mais difícil que saber, e terminar é mais difícil que fazer</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudência até o fim (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Fazer é mais difícil do que saber, e terminar é mais difícil do que fazer</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudência até ao fim (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Fare è più difficile che sapere, e portare a termine più difficile che fare</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudenza fino alla fine (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Hacer es más difícil que saber, y terminar es más difícil que hacer</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Prudencia hasta el fin (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>Мэдэхээс хийх нь хэцүү, хийхээс дуусгах нь хэцүү</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Эцэст нь болгоомжлох» (Вэй Чжэн)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1115,24 +2123,96 @@
           <t>鑒形之美惡，必就於止水；鑒國之安危，必取於亡國</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Judge your face in still water; judge a state's safety by states that have fallen</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Law (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>形の美悪を鑒みるは、必ず止水に就き、国の安危を鑒みるは、必ず亡国に取る</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』刑法（魏徴）</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>鑒形之美惡，必就於止水；鑒國之安危，必取於亡國</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·刑法》（魏徵）</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>鉴形之美恶，必就于止水；鉴国之安危，必取于亡国</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·刑法》（魏征）</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>O rosto se vê na água parada; o destino de um reino, nos reinos caídos</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Leis e penas (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>O rosto vê-se na água parada; o destino de um reino, nos reinos caídos</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Leis e penas (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Il volto si specchia nell'acqua ferma; le sorti di un regno, nei regni caduti</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Leggi e pene (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>El rostro se mira en el agua quieta; la suerte de un reino, en los reinos caídos</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Leyes y penas (Wei Zheng)</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Царайгаа тогтуун усанд, улсын амар аюулыг мөхсөн улсад харж тольд</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Хууль цааз» (Вэй Чжэн)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1153,24 +2233,96 @@
           <t>流水清濁，在其源也</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Whether flowing water runs clear or muddy depends on its source</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Sincerity (Emperor Taizong)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>流水の清濁は、其の源に在り</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』誠信（太宗）</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>流水清濁，在其源也</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·誠信》（太宗）</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>流水清浊，在其源也</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·诚信》（太宗）</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Se a água corre limpa ou turva, depende da nascente</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Sinceridade (imperador Taizong)</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Se a água corre limpa ou turva, depende da nascente</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Sinceridade (imperador Taizong)</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Che l'acqua scorra limpida o torbida dipende dalla sorgente</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Sincerità (imperatore Taizong)</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Que el agua corra clara o turbia depende de su fuente</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Sinceridad (emperador Taizong)</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Урсах усны тунгалаг, булингар нь эх булгаасаа шалтгаална</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Үнэнч итгэл» (Тайцзун)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1191,24 +2343,96 @@
           <t>小人之幸，君子之不幸</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="n"/>
-      <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>A petty man's good fortune is a gentleman's misfortune</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Pardons (Emperor Taizong)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>小人の幸いは、君子の不幸なり</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』赦令（太宗）</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>小人之幸，君子之不幸</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·赦令》（太宗）</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>小人之幸，君子之不幸</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·赦令》（太宗）</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>A sorte do homem mesquinho é o infortúnio do homem nobre</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Indultos (imperador Taizong)</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>A sorte do homem mesquinho é o infortúnio do homem nobre</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Indultos (imperador Taizong)</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>La fortuna dell'uomo meschino è la sventura dell'uomo nobile</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Amnistie (imperatore Taizong)</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>La fortuna del hombre mezquino es la desgracia del hombre noble</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Indultos (emperador Taizong)</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Өчүүхэн хүний аз бол эрхэм хүний гай</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Өршөөл» (Тайцзун)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1229,24 +2453,96 @@
           <t>戰勝易，守勝難</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
-      <c r="R19" s="2" t="n"/>
-      <c r="S19" s="2" t="n"/>
-      <c r="T19" s="2" t="n"/>
-      <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>To win in battle is easy; to preserve the victory is hard</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Wuzi, Planning for the State</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>戦いて勝つは易く、勝ちを守るは難し</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>『呉子』図国</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>戰勝易，守勝難</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>《吳子·圖國》</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>战胜易，守胜难</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>《吴子·图国》</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Vencer a batalha é fácil; conservar a vitória é difícil</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Wuzi, Planejar o Estado</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Vencer a batalha é fácil; conservar a vitória é difícil</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Wuzi, Planear o Estado</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Vincere in battaglia è facile; conservare la vittoria è difficile</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Wuzi, Pianificare lo Stato</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Vencer en batalla es fácil; conservar la victoria es difícil</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Wuzi, Planificar el Estado</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Дайнд ялах амархан, ялалтаа хамгаалах хэцүү</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>У-цзы, «Улсыг төлөвлөх»</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1267,24 +2563,96 @@
           <t>兵惡不戢，武貴止戈</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="n"/>
-      <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The bane of war is that it never ends; true valor lies in laying down the spear</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Campaigns (Fang Xuanling)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>兵は戢めざるを悪み、武は戈を止むるを貴ぶ</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>『貞観政要』征伐（房玄齢）</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>兵惡不戢，武貴止戈</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>《貞觀政要·征伐》（房玄齡）</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>兵恶不戢，武贵止戈</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>《贞观政要·征伐》（房玄龄）</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>O pior da guerra é não ter fim; o verdadeiro valor está em depor a lança</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Campanhas (Fang Xuanling)</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>O pior da guerra é não ter fim; o verdadeiro valor está em depor a lança</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Campanhas (Fang Xuanling)</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Il peggio della guerra è non avere fine; il vero valore sta nel deporre la lancia</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Campagne (Fang Xuanling)</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>Lo peor de la guerra es no tener fin; el valor verdadero está en deponer la lanza</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Zhenguan Zhengyao, Campañas (Fang Xuanling)</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Дайны хор нь зогсохгүйд, жинхэнэ эр зориг нь жадаа хураахад</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Чжэньгуань чжэнъяо, «Дайн» (Фан Сюаньлин)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1305,24 +2673,96 @@
           <t>以蒙養正，以明夷蒞眾</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
-      <c r="T21" s="2" t="n"/>
-      <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Foster the right by seeming simple; govern the people with wisdom hidden</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, hexagrams Meng and Ming Yi</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>蒙を以て正を養い、明夷を以て衆に蒞む</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>『易経』蒙卦・明夷卦</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>以蒙養正，以明夷蒞眾</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>《周易》蒙卦、明夷卦</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>以蒙养正，以明夷莅众</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>《周易》蒙卦、明夷卦</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Cultive o que é reto parecendo simples; governe o povo com seu saber oculto</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, hexagramas Meng e Ming Yi</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Cultiva o que é reto parecendo simples; governa o povo com o teu saber oculto</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, hexagramas Meng e Ming Yi</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Coltiva il giusto sembrando semplice; governa il popolo col sapere celato</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, esagrammi Meng e Ming Yi</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Cultiva lo recto pareciendo simple; gobierna al pueblo con tu saber oculto</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>I Ching, hexagramas Meng y Ming Yi</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Энгийн мэт байж зөвийг тэтгэ, мэргэн ухаанаа нууж ардыг захир</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>И цзин, Мэн ба Мин и зурлага</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
